--- a/Output/PowerPoint_Figures/Fig_2/Fig_2h_Epirubicin_TC50_data.xlsx
+++ b/Output/PowerPoint_Figures/Fig_2/Fig_2h_Epirubicin_TC50_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Concentration</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>O2_mean</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>O2_std</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>N_wells</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Consumption</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Consumption_std</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Timepoint_h</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Excluded_Wells</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>TC50_mM</t>
         </is>
@@ -465,21 +473,33 @@
         <v>0.094</v>
       </c>
       <c r="B2" t="n">
-        <v>16.92895</v>
-      </c>
-      <c r="C2" t="n">
+        <v>31.16611</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
         <v>100</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>32</v>
-      </c>
       <c r="F2" t="n">
-        <v>0.7262212733973268</v>
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4, 10, 11, 13, 15]</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4527258331708474</v>
       </c>
     </row>
     <row r="3">
@@ -487,21 +507,33 @@
         <v>0.19</v>
       </c>
       <c r="B3" t="n">
-        <v>28.90548</v>
-      </c>
-      <c r="C3" t="n">
-        <v>65.79839968381482</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
-        </is>
+        <v>32.01667</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>95.47211032685279</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7262212733973268</v>
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4, 10, 11, 13, 15]</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4527258331708474</v>
       </c>
     </row>
     <row r="4">
@@ -509,21 +541,35 @@
         <v>0.38</v>
       </c>
       <c r="B4" t="n">
-        <v>22.13255575</v>
+        <v>37.12627</v>
       </c>
       <c r="C4" t="n">
-        <v>85.13996591128624</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
-        </is>
+        <v>8.746684609107611</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>68.27155413573982</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7262212733973268</v>
+        <v>46.56229180287588</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4, 10, 11, 13, 15]</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4527258331708474</v>
       </c>
     </row>
     <row r="5">
@@ -531,21 +577,35 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>36.19013</v>
+        <v>47.85111999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>44.99548867843195</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
-        </is>
+        <v>0.5863753693667524</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>11.17865350432877</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7262212733973268</v>
+        <v>3.1215234428419</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4, 10, 11, 13, 15]</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4527258331708474</v>
       </c>
     </row>
     <row r="6">
@@ -553,21 +613,35 @@
         <v>1.5</v>
       </c>
       <c r="B6" t="n">
-        <v>45.744775</v>
+        <v>47.774305</v>
       </c>
       <c r="C6" t="n">
-        <v>17.71011057199903</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
-        </is>
+        <v>0.3132836594046995</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>11.58757215232866</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7262212733973268</v>
+        <v>1.667741071981178</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>40</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4, 10, 11, 13, 15]</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4527258331708474</v>
       </c>
     </row>
     <row r="7">
@@ -575,65 +649,69 @@
         <v>3</v>
       </c>
       <c r="B7" t="n">
-        <v>46.64726</v>
+        <v>49.79066</v>
       </c>
       <c r="C7" t="n">
-        <v>15.13286730860366</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
-        </is>
+        <v>1.208516199725925</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>0.8536639249269617</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7262212733973268</v>
+        <v>6.433441521550678</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4, 10, 11, 13, 15]</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4527258331708474</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>42.67289666666667</v>
-      </c>
-      <c r="C8" t="n">
-        <v>26.48253087876699</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
-        </is>
+        <v>49.95102</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7262212733973268</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>12</v>
-      </c>
-      <c r="B9" t="n">
-        <v>51.946405</v>
-      </c>
-      <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>C:\Users\NoahB\Documents\HebrewU Bioengineering\Cardiac_RODEO\Cleaned_Data\DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>32</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.7262212733973268</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>/Users/noahb/Documents/HebrewU Bioengineering/Cardiac_RODEO/Cleaned_Data/DrugScreen19.11.25_compiled_O2_mean.xlsx</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>40</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[0, 2, 3, 4, 10, 11, 13, 15]</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4527258331708474</v>
       </c>
     </row>
   </sheetData>
